--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
@@ -491,14 +491,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>De la: ______________________ · telefon: ______________ · e-mail: ______________</t>
+          <t>De la: George Șerban · telefon: 0765468714 · e-mail: george357ro@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data cererii: ____ . ____ . 2026</t>
+          <t>Data cererii: 6 octombrie 2026</t>
         </is>
       </c>
     </row>

--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -624,34 +624,63 @@
       <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Cireș sălbatic</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Prunus avium</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7">
-        <f>SUM(D11:D12)</f>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7">
+        <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7">
-        <f>SUM(G11:G12)</f>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7">
+        <f>SUM(G11:G13)</f>
         <v/>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Vă rugăm să precizați: costul transportului la Crucea sau adresa de ridicare, termenul de valabilitate al ofertei, dacă puteți rezerva cantitățile până la confirmare, și eventualele specii pe care nu le aveți (cu propuneri de înlocuire).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Vă mulțumim.</t>
         </is>
@@ -661,8 +690,8 @@
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A15:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-doi-cocosi-srl.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
